--- a/output/daily_screen_20261027.xlsx
+++ b/output/daily_screen_20261027.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -703,7 +703,7 @@
         <v>19.75</v>
       </c>
       <c r="R2" t="n">
-        <v>49445359</v>
+        <v>49291390</v>
       </c>
       <c r="S2" t="n">
         <v>19.60999984741211</v>
@@ -813,7 +813,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -845,7 +845,7 @@
         <v>100.5</v>
       </c>
       <c r="R3" t="n">
-        <v>2631762</v>
+        <v>2617057</v>
       </c>
       <c r="S3" t="n">
         <v>100.2199996948242</v>
@@ -951,7 +951,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -983,7 +983,7 @@
         <v>247.5</v>
       </c>
       <c r="R4" t="n">
-        <v>52590870</v>
+        <v>52105881</v>
       </c>
       <c r="S4" t="n">
         <v>245.8</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1123,7 +1123,7 @@
         <v>327.5</v>
       </c>
       <c r="R5" t="n">
-        <v>15061382</v>
+        <v>14877430</v>
       </c>
       <c r="S5" t="n">
         <v>324.1</v>
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>56.8</v>
+        <v>58.2</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1231,15 +1231,15 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>6979000</v>
+        <v>7636000</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
@@ -1248,13 +1248,13 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>6899000</v>
+        <v>6979000</v>
       </c>
       <c r="N6" t="n">
-        <v>80000</v>
+        <v>657000</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01159588346137121</v>
+        <v>0.09413956154176815</v>
       </c>
       <c r="P6" t="n">
         <v>1080</v>
@@ -1263,7 +1263,7 @@
         <v>1080</v>
       </c>
       <c r="R6" t="n">
-        <v>9249607</v>
+        <v>8987041</v>
       </c>
       <c r="S6" t="n">
         <v>1138</v>
@@ -1367,11 +1367,11 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>9968000</v>
+        <v>11944000</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
@@ -1384,13 +1384,13 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>8895000</v>
+        <v>9968000</v>
       </c>
       <c r="N7" t="n">
-        <v>1073000</v>
+        <v>1976000</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1206295671725689</v>
+        <v>0.1982343499197432</v>
       </c>
       <c r="P7" t="n">
         <v>651</v>
@@ -1399,7 +1399,7 @@
         <v>651</v>
       </c>
       <c r="R7" t="n">
-        <v>25585620</v>
+        <v>25176454</v>
       </c>
       <c r="S7" t="n">
         <v>660.6</v>
@@ -1480,12 +1480,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1494,24 +1494,24 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>54.6</v>
+        <v>53.40000000000001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>13046000</v>
+        <v>8937000</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
@@ -1520,76 +1520,76 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>12671000</v>
+        <v>8937000</v>
       </c>
       <c r="N8" t="n">
-        <v>375000</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0295951385052482</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2400</v>
+        <v>1255</v>
       </c>
       <c r="Q8" t="n">
-        <v>2400</v>
+        <v>1255</v>
       </c>
       <c r="R8" t="n">
-        <v>35766965</v>
+        <v>10198034</v>
       </c>
       <c r="S8" t="n">
-        <v>2399</v>
+        <v>1286</v>
       </c>
       <c r="T8" t="n">
-        <v>2476.5</v>
+        <v>1375.25</v>
       </c>
       <c r="U8" t="n">
-        <v>2481.5</v>
+        <v>1373</v>
       </c>
       <c r="V8" t="n">
-        <v>2424.348356119792</v>
+        <v>1210</v>
       </c>
       <c r="W8" t="n">
-        <v>-25.50850595834754</v>
+        <v>-14.10378787195941</v>
       </c>
       <c r="X8" t="n">
-        <v>-11.47065173465664</v>
+        <v>18.543737774572</v>
       </c>
       <c r="Y8" t="n">
-        <v>-14.0378542236909</v>
+        <v>-32.64752564653142</v>
       </c>
       <c r="Z8" t="n">
-        <v>-17.90009387185703</v>
+        <v>-33.65749788527849</v>
       </c>
       <c r="AA8" t="b">
         <v>1</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.04000000000000004</v>
+        <v>0.03719008264462809</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.09412034967687477</v>
+        <v>0.4277588168373152</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.004352818422789451</v>
+        <v>0.07283726422183867</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.01387263841941411</v>
+        <v>0.3197658287410263</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.009519819996624657</v>
+        <v>-0.2469285645191877</v>
       </c>
       <c r="AG8" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AH8" t="n">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK8" t="b">
         <v>0</v>
@@ -1601,13 +1601,13 @@
         <v>1</v>
       </c>
       <c r="AN8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>2558.4</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>2555.53</v>
+        <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1618,12 +1618,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1632,24 +1632,24 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53.40000000000001</v>
+        <v>51.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>8937000</v>
+        <v>19739000</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K9" t="b">
         <v>1</v>
@@ -1658,76 +1658,76 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>8937000</v>
+        <v>19689000</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.002539489054802174</v>
       </c>
       <c r="P9" t="n">
-        <v>1255</v>
+        <v>1060</v>
       </c>
       <c r="Q9" t="n">
-        <v>1255</v>
+        <v>1060</v>
       </c>
       <c r="R9" t="n">
-        <v>10348912</v>
+        <v>29151623</v>
       </c>
       <c r="S9" t="n">
-        <v>1286</v>
+        <v>1077</v>
       </c>
       <c r="T9" t="n">
-        <v>1375.25</v>
+        <v>1177.25</v>
       </c>
       <c r="U9" t="n">
-        <v>1373</v>
+        <v>1182.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1210</v>
+        <v>1061.933333333333</v>
       </c>
       <c r="W9" t="n">
-        <v>-14.10378787195941</v>
+        <v>-23.38602191958125</v>
       </c>
       <c r="X9" t="n">
-        <v>18.543737774572</v>
+        <v>-2.819302364148833</v>
       </c>
       <c r="Y9" t="n">
-        <v>-32.64752564653142</v>
+        <v>-20.56671955543242</v>
       </c>
       <c r="Z9" t="n">
-        <v>-33.65749788527849</v>
+        <v>-22.30077112154821</v>
       </c>
       <c r="AA9" t="b">
         <v>1</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03719008264462809</v>
+        <v>-0.08620689655172409</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.4277588168373152</v>
+        <v>0.5406976744186047</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.07283726422183867</v>
+        <v>-0.0505597149745135</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.3197658287410263</v>
+        <v>0.4327046863223158</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.2469285645191877</v>
+        <v>-0.4832644012968293</v>
       </c>
       <c r="AG9" t="n">
+        <v>50</v>
+      </c>
+      <c r="AH9" t="n">
         <v>88</v>
       </c>
-      <c r="AH9" t="n">
-        <v>78</v>
-      </c>
       <c r="AI9" t="b">
         <v>0</v>
       </c>
       <c r="AJ9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="b">
         <v>0</v>
@@ -1742,10 +1742,8 @@
         <v>0</v>
       </c>
       <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AP9" t="n">
+        <v>1308.42</v>
       </c>
     </row>
     <row r="10">
@@ -1779,7 +1777,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1811,7 +1809,7 @@
         <v>278.5</v>
       </c>
       <c r="R10" t="n">
-        <v>18593088</v>
+        <v>18438940</v>
       </c>
       <c r="S10" t="n">
         <v>292.8</v>
@@ -1896,12 +1894,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1910,102 +1908,102 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>46.8</v>
+        <v>46</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>7556450</v>
+        <v>121000</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="K11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="b">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>6587450</v>
+        <v>121000</v>
       </c>
       <c r="N11" t="n">
-        <v>969000</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1470978906860773</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>269</v>
+        <v>1285</v>
       </c>
       <c r="Q11" t="n">
-        <v>269</v>
+        <v>1285</v>
       </c>
       <c r="R11" t="n">
-        <v>25732274</v>
+        <v>2066666</v>
       </c>
       <c r="S11" t="n">
-        <v>266.3</v>
+        <v>1291</v>
       </c>
       <c r="T11" t="n">
-        <v>286.55</v>
+        <v>1400.25</v>
       </c>
       <c r="U11" t="n">
-        <v>288.3</v>
+        <v>1396.25</v>
       </c>
       <c r="V11" t="n">
-        <v>266.5</v>
+        <v>1285.028885904948</v>
       </c>
       <c r="W11" t="n">
-        <v>-6.439246733244204</v>
+        <v>-30.09157402581354</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.198326649822184</v>
+        <v>6.281712615044271</v>
       </c>
       <c r="Y11" t="n">
-        <v>-3.24092008342202</v>
+        <v>-36.37328664085781</v>
       </c>
       <c r="Z11" t="n">
-        <v>-4.489412957966038</v>
+        <v>-41.34986774007167</v>
       </c>
       <c r="AA11" t="b">
         <v>1</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.1151315789473685</v>
+        <v>0.06639004149377592</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.2658823529411765</v>
+        <v>0.4621730953688772</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.07948439737015789</v>
+        <v>0.1020372230709865</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.1578893648448876</v>
+        <v>0.3541801072725883</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.2373737622150455</v>
+        <v>-0.2521428842016018</v>
       </c>
       <c r="AG11" t="n">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="AH11" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="AI11" t="b">
         <v>0</v>
       </c>
       <c r="AJ11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK11" t="b">
         <v>0</v>
@@ -2017,13 +2015,13 @@
         <v>1</v>
       </c>
       <c r="AN11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>305.58</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>329.47</v>
+        <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -2034,12 +2032,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2048,7 +2046,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>46</v>
+        <v>45.2</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2057,15 +2055,15 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>121000</v>
+        <v>1000</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
@@ -2074,7 +2072,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>121000</v>
+        <v>1000</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -2083,61 +2081,61 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1285</v>
+        <v>520</v>
       </c>
       <c r="Q12" t="n">
-        <v>1285</v>
+        <v>520</v>
       </c>
       <c r="R12" t="n">
-        <v>2121638</v>
+        <v>44188301</v>
       </c>
       <c r="S12" t="n">
-        <v>1291</v>
+        <v>555.8</v>
       </c>
       <c r="T12" t="n">
-        <v>1400.25</v>
+        <v>549.55</v>
       </c>
       <c r="U12" t="n">
-        <v>1396.25</v>
+        <v>547.2</v>
       </c>
       <c r="V12" t="n">
-        <v>1285.028885904948</v>
+        <v>498.7333333333333</v>
       </c>
       <c r="W12" t="n">
-        <v>-30.09157402581354</v>
+        <v>4.908876771783525</v>
       </c>
       <c r="X12" t="n">
-        <v>6.281712615044271</v>
+        <v>11.22699949399457</v>
       </c>
       <c r="Y12" t="n">
-        <v>-36.37328664085781</v>
+        <v>-6.318122722211049</v>
       </c>
       <c r="Z12" t="n">
-        <v>-41.34986774007167</v>
+        <v>-2.170850959171391</v>
       </c>
       <c r="AA12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.06639004149377592</v>
+        <v>0.09936575052854124</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.4621730953688772</v>
+        <v>0.2855377008652658</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.1020372230709865</v>
+        <v>0.1350129321057518</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.3541801072725883</v>
+        <v>0.1775447127689769</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.2521428842016018</v>
+        <v>-0.04253178066322505</v>
       </c>
       <c r="AG12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH12" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="AI12" t="b">
         <v>0</v>
@@ -2152,12 +2150,14 @@
         <v>0</v>
       </c>
       <c r="AM12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>591.76</v>
+      </c>
       <c r="AP12" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -2172,12 +2172,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2186,7 +2186,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>45.2</v>
+        <v>44.6</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2195,24 +2195,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1000</v>
+        <v>13046000</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="K13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="b">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1000</v>
+        <v>13046000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -2221,67 +2221,67 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>520</v>
+        <v>2400</v>
       </c>
       <c r="Q13" t="n">
-        <v>520</v>
+        <v>2400</v>
       </c>
       <c r="R13" t="n">
-        <v>45376020</v>
+        <v>33964182</v>
       </c>
       <c r="S13" t="n">
-        <v>555.8</v>
+        <v>2399</v>
       </c>
       <c r="T13" t="n">
-        <v>549.55</v>
+        <v>2476.5</v>
       </c>
       <c r="U13" t="n">
-        <v>547.2</v>
+        <v>2481.5</v>
       </c>
       <c r="V13" t="n">
-        <v>498.7333333333333</v>
+        <v>2424.348356119792</v>
       </c>
       <c r="W13" t="n">
-        <v>4.908876771783525</v>
+        <v>-25.50850595855854</v>
       </c>
       <c r="X13" t="n">
-        <v>11.22699949399457</v>
+        <v>-11.47065173507779</v>
       </c>
       <c r="Y13" t="n">
-        <v>-6.318122722211049</v>
+        <v>-14.03785422348076</v>
       </c>
       <c r="Z13" t="n">
-        <v>-2.170850959171391</v>
+        <v>-17.90009387162073</v>
       </c>
       <c r="AA13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.09936575052854124</v>
+        <v>-0.04000000000000004</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.2855377008652658</v>
+        <v>0.09412034967687477</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.1350129321057518</v>
+        <v>-0.004352818422789451</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.1775447127689769</v>
+        <v>-0.01387263841941411</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.04253178066322505</v>
+        <v>0.009519819996624657</v>
       </c>
       <c r="AG13" t="n">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AH13" t="n">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="AI13" t="b">
         <v>0</v>
       </c>
       <c r="AJ13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="b">
         <v>0</v>
@@ -2290,18 +2290,16 @@
         <v>0</v>
       </c>
       <c r="AM13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN13" t="b">
         <v>1</v>
       </c>
       <c r="AO13" t="n">
-        <v>591.76</v>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+        <v>2558.4</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>2555.53</v>
       </c>
     </row>
     <row r="14">
@@ -2312,12 +2310,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2326,7 +2324,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>43</v>
+        <v>42.2</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2335,24 +2333,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>19689000</v>
+        <v>4827000</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="K14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>19689000</v>
+        <v>4827000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2361,61 +2359,61 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1060</v>
+        <v>248</v>
       </c>
       <c r="Q14" t="n">
-        <v>1060</v>
+        <v>248</v>
       </c>
       <c r="R14" t="n">
-        <v>29758483</v>
+        <v>16611569</v>
       </c>
       <c r="S14" t="n">
-        <v>1077</v>
+        <v>250.6</v>
       </c>
       <c r="T14" t="n">
-        <v>1177.25</v>
+        <v>253.575</v>
       </c>
       <c r="U14" t="n">
-        <v>1182.25</v>
+        <v>253.775</v>
       </c>
       <c r="V14" t="n">
-        <v>1061.933333333333</v>
+        <v>232.8083333333333</v>
       </c>
       <c r="W14" t="n">
-        <v>-23.38602191958125</v>
+        <v>-0.4276564339809283</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.819302364148833</v>
+        <v>2.707088558435337</v>
       </c>
       <c r="Y14" t="n">
-        <v>-20.56671955543242</v>
+        <v>-3.134744992416265</v>
       </c>
       <c r="Z14" t="n">
-        <v>-22.30077112154821</v>
+        <v>-3.165791552069547</v>
       </c>
       <c r="AA14" t="b">
         <v>1</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.08620689655172409</v>
+        <v>-0.01587301587301593</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.5406976744186047</v>
+        <v>0.4850299401197604</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.0505597149745135</v>
+        <v>0.01977416570419466</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.4327046863223158</v>
+        <v>0.3770369520234715</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.4832644012968293</v>
+        <v>-0.3572627863192769</v>
       </c>
       <c r="AG14" t="n">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="AH14" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="AI14" t="b">
         <v>0</v>
@@ -2433,11 +2431,13 @@
         <v>1</v>
       </c>
       <c r="AN14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>283.71</v>
+      </c>
       <c r="AP14" t="n">
-        <v>1308.42</v>
+        <v>251.87</v>
       </c>
     </row>
     <row r="15">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2471,15 +2471,15 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>4827000</v>
+        <v>1000</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
@@ -2488,7 +2488,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4827000</v>
+        <v>1000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2497,61 +2497,61 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>248</v>
+        <v>6000</v>
       </c>
       <c r="Q15" t="n">
-        <v>248</v>
+        <v>6000</v>
       </c>
       <c r="R15" t="n">
-        <v>16776474</v>
+        <v>2633916</v>
       </c>
       <c r="S15" t="n">
-        <v>250.6</v>
+        <v>6099</v>
       </c>
       <c r="T15" t="n">
-        <v>253.575</v>
+        <v>6451</v>
       </c>
       <c r="U15" t="n">
-        <v>253.775</v>
+        <v>6460.5</v>
       </c>
       <c r="V15" t="n">
-        <v>232.8083333333333</v>
+        <v>6000.348087565104</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.4276564339809283</v>
+        <v>-124.2560250752931</v>
       </c>
       <c r="X15" t="n">
-        <v>2.707088558435337</v>
+        <v>-31.00814777542721</v>
       </c>
       <c r="Y15" t="n">
-        <v>-3.134744992416265</v>
+        <v>-93.24787729986591</v>
       </c>
       <c r="Z15" t="n">
-        <v>-3.165791552069547</v>
+        <v>-93.08022660698893</v>
       </c>
       <c r="AA15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.01587301587301593</v>
+        <v>-0.03069466882067851</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.4850299401197604</v>
+        <v>0.5726762853585796</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.01977416570419466</v>
+        <v>0.004952512756532079</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.3770369520234715</v>
+        <v>0.4646832972622907</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.3572627863192769</v>
+        <v>-0.4597307845057587</v>
       </c>
       <c r="AG15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AH15" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="AI15" t="b">
         <v>0</v>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="AM15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>283.71</v>
+        <v>7056</v>
       </c>
       <c r="AP15" t="n">
-        <v>251.87</v>
+        <v>6719.74</v>
       </c>
     </row>
     <row r="16">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2600,7 +2600,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>42.2</v>
+        <v>40.8</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2609,15 +2609,15 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1000</v>
+        <v>3921000</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="K16" t="b">
         <v>0</v>
@@ -2626,7 +2626,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1000</v>
+        <v>3921000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2635,67 +2635,67 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>6000</v>
+        <v>87.69999694824219</v>
       </c>
       <c r="Q16" t="n">
-        <v>6000</v>
+        <v>87.69999694824219</v>
       </c>
       <c r="R16" t="n">
-        <v>2773940</v>
+        <v>2831267</v>
       </c>
       <c r="S16" t="n">
-        <v>6099</v>
+        <v>90</v>
       </c>
       <c r="T16" t="n">
-        <v>6451</v>
+        <v>88.7550006866455</v>
       </c>
       <c r="U16" t="n">
-        <v>6460.5</v>
+        <v>88.51000099182129</v>
       </c>
       <c r="V16" t="n">
-        <v>6000.348087565104</v>
+        <v>85.06666679382325</v>
       </c>
       <c r="W16" t="n">
-        <v>-124.2560250752931</v>
+        <v>0.7265338970744608</v>
       </c>
       <c r="X16" t="n">
-        <v>-31.00814777542713</v>
+        <v>1.509267513139483</v>
       </c>
       <c r="Y16" t="n">
-        <v>-93.24787729986599</v>
+        <v>-0.782733616065022</v>
       </c>
       <c r="Z16" t="n">
-        <v>-93.08022660698904</v>
+        <v>-0.5196039515255642</v>
       </c>
       <c r="AA16" t="b">
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0.03069466882067851</v>
+        <v>0.05917866806624894</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.5726762853585796</v>
+        <v>0.1017587767511641</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.004952512756532079</v>
+        <v>0.09482584964345953</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.4646832972622907</v>
+        <v>-0.006234211345124807</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.4597307845057587</v>
+        <v>0.1010600609885843</v>
       </c>
       <c r="AG16" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="AH16" t="n">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="AI16" t="b">
         <v>0</v>
       </c>
       <c r="AJ16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK16" t="b">
         <v>0</v>
@@ -2707,13 +2707,15 @@
         <v>0</v>
       </c>
       <c r="AN16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO16" t="n">
-        <v>7056</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>6719.74</v>
+        <v>96.65000000000001</v>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -2724,12 +2726,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2738,7 +2740,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>40.8</v>
+        <v>39.8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2747,15 +2749,15 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>3921000</v>
+        <v>6003000</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K17" t="b">
         <v>0</v>
@@ -2764,7 +2766,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3921000</v>
+        <v>6003000</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2773,82 +2775,84 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>87.69999694824219</v>
+        <v>190.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>87.69999694824219</v>
+        <v>190.5</v>
       </c>
       <c r="R17" t="n">
-        <v>2870815</v>
+        <v>22416629</v>
       </c>
       <c r="S17" t="n">
+        <v>190.9</v>
+      </c>
+      <c r="T17" t="n">
+        <v>187.025</v>
+      </c>
+      <c r="U17" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="V17" t="n">
+        <v>185.5333333333333</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.290218095677432</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.5864765284235762</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.7037415672538554</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.7464855548500338</v>
+      </c>
+      <c r="AA17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.05833333333333335</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.1238938053097345</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.09398051491054393</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.01590081721344561</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.07807969769709833</v>
+      </c>
+      <c r="AG17" t="n">
         <v>90</v>
       </c>
-      <c r="T17" t="n">
-        <v>88.7550006866455</v>
-      </c>
-      <c r="U17" t="n">
-        <v>88.51000099182129</v>
-      </c>
-      <c r="V17" t="n">
-        <v>85.06666679382325</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0.7265338970744608</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.509267513139483</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>-0.782733616065022</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>-0.5196039515255642</v>
-      </c>
-      <c r="AA17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0.05917866806624894</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0.1017587767511641</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0.09482584964345953</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>-0.006234211345124807</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0.1010600609885843</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>94</v>
-      </c>
       <c r="AH17" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AI17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ17" t="b">
         <v>1</v>
       </c>
       <c r="AK17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM17" t="b">
         <v>0</v>
       </c>
       <c r="AN17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>96.65000000000001</v>
+        <v>0</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
@@ -2864,12 +2868,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2882,20 +2886,20 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>6003000</v>
+        <v>923000</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="K18" t="b">
         <v>0</v>
@@ -2904,82 +2908,82 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>6003000</v>
+        <v>852000</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>71000</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="P18" t="n">
-        <v>190.5</v>
+        <v>7430</v>
       </c>
       <c r="Q18" t="n">
-        <v>190.5</v>
+        <v>7430</v>
       </c>
       <c r="R18" t="n">
-        <v>22637098</v>
+        <v>2291700</v>
       </c>
       <c r="S18" t="n">
-        <v>190.9</v>
+        <v>7669</v>
       </c>
       <c r="T18" t="n">
-        <v>187.025</v>
+        <v>7992.5</v>
       </c>
       <c r="U18" t="n">
-        <v>186.5</v>
+        <v>8040.25</v>
       </c>
       <c r="V18" t="n">
-        <v>185.5333333333333</v>
+        <v>6463</v>
       </c>
       <c r="W18" t="n">
-        <v>1.290218095677432</v>
+        <v>-30.32926562784814</v>
       </c>
       <c r="X18" t="n">
-        <v>0.5864765284235762</v>
+        <v>113.5701033116136</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.7037415672538554</v>
+        <v>-143.8993689394617</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.7464855548500338</v>
+        <v>-140.2217805557706</v>
       </c>
       <c r="AA18" t="b">
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.05833333333333335</v>
+        <v>-0.1138938580799046</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.1238938053097345</v>
+        <v>1.254931714719272</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.09398051491054393</v>
+        <v>-0.07824667650269401</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.01590081721344561</v>
+        <v>1.146938726622983</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.07807969769709833</v>
+        <v>-1.225185403125677</v>
       </c>
       <c r="AG18" t="n">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="AH18" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="AI18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="b">
         <v>0</v>
@@ -2987,15 +2991,9 @@
       <c r="AN18" t="b">
         <v>0</v>
       </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP18" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="n">
+        <v>9117.110000000001</v>
       </c>
     </row>
     <row r="19">
@@ -3029,7 +3027,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -3037,7 +3035,7 @@
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K19" t="b">
         <v>0</v>
@@ -3061,7 +3059,7 @@
         <v>1465</v>
       </c>
       <c r="R19" t="n">
-        <v>5098695</v>
+        <v>4969284</v>
       </c>
       <c r="S19" t="n">
         <v>1558</v>
@@ -3142,12 +3140,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3156,24 +3154,24 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>39.4</v>
+        <v>38.2</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>6537000</v>
+        <v>501000</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="K20" t="b">
         <v>0</v>
@@ -3182,70 +3180,70 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>6457000</v>
+        <v>501000</v>
       </c>
       <c r="N20" t="n">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.01238965463837696</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3130</v>
+        <v>216</v>
       </c>
       <c r="Q20" t="n">
-        <v>3130</v>
+        <v>216</v>
       </c>
       <c r="R20" t="n">
-        <v>2778810</v>
+        <v>23777890</v>
       </c>
       <c r="S20" t="n">
-        <v>3196</v>
+        <v>229.8</v>
       </c>
       <c r="T20" t="n">
-        <v>3363.75</v>
+        <v>236.95</v>
       </c>
       <c r="U20" t="n">
-        <v>3380.75</v>
+        <v>237.35</v>
       </c>
       <c r="V20" t="n">
-        <v>3185.9912109375</v>
+        <v>225.2333333333333</v>
       </c>
       <c r="W20" t="n">
-        <v>-64.94596194307451</v>
+        <v>-3.163724079880438</v>
       </c>
       <c r="X20" t="n">
-        <v>-33.7312883593824</v>
+        <v>1.210105544070594</v>
       </c>
       <c r="Y20" t="n">
-        <v>-31.2146735836921</v>
+        <v>-4.373829623951033</v>
       </c>
       <c r="Z20" t="n">
-        <v>-32.99125700943229</v>
+        <v>-3.407192547424745</v>
       </c>
       <c r="AA20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0.09798270893371763</v>
+        <v>-0.0357142857142857</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.5028965429281285</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.06233552735650705</v>
+        <v>-6.710413707511353e-05</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.3949035548318396</v>
+        <v>0.1551649066405532</v>
       </c>
       <c r="AF20" t="n">
-        <v>-0.4572390821883466</v>
+        <v>-0.1552320107776283</v>
       </c>
       <c r="AG20" t="n">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="AH20" t="n">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="AI20" t="b">
         <v>0</v>
@@ -3260,16 +3258,14 @@
         <v>0</v>
       </c>
       <c r="AM20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>3486.82</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO20" t="inlineStr"/>
       <c r="AP20" t="n">
-        <v>3801.05</v>
+        <v>244.55</v>
       </c>
     </row>
     <row r="21">
@@ -3280,12 +3276,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3294,24 +3290,24 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>38.2</v>
+        <v>37.2</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>501000</v>
+        <v>1126000</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K21" t="b">
         <v>0</v>
@@ -3320,70 +3316,70 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>501000</v>
+        <v>969000</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>157000</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>0.1620227038183694</v>
       </c>
       <c r="P21" t="n">
-        <v>216</v>
+        <v>2250</v>
       </c>
       <c r="Q21" t="n">
-        <v>216</v>
+        <v>2250</v>
       </c>
       <c r="R21" t="n">
-        <v>24203493</v>
+        <v>1195174</v>
       </c>
       <c r="S21" t="n">
-        <v>229.8</v>
+        <v>2321</v>
       </c>
       <c r="T21" t="n">
-        <v>236.95</v>
+        <v>2343.5</v>
       </c>
       <c r="U21" t="n">
-        <v>237.35</v>
+        <v>2361</v>
       </c>
       <c r="V21" t="n">
-        <v>225.2333333333333</v>
+        <v>2100.230332438151</v>
       </c>
       <c r="W21" t="n">
-        <v>-3.163724079880438</v>
+        <v>-2.166083020384121</v>
       </c>
       <c r="X21" t="n">
-        <v>1.210105544070594</v>
+        <v>3.145393600799783</v>
       </c>
       <c r="Y21" t="n">
-        <v>-4.373829623951033</v>
+        <v>-5.311476621183904</v>
       </c>
       <c r="Z21" t="n">
-        <v>-3.407192547424745</v>
+        <v>1.524106016444781</v>
       </c>
       <c r="AA21" t="b">
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>-0.0357142857142857</v>
+        <v>-0.1346153846153846</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.263157894736842</v>
+        <v>0.791094203859015</v>
       </c>
       <c r="AD21" t="n">
-        <v>-6.710413707511353e-05</v>
+        <v>-0.098968203038174</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.1551649066405532</v>
+        <v>0.6831012157627261</v>
       </c>
       <c r="AF21" t="n">
-        <v>-0.1552320107776283</v>
+        <v>-0.7820694188009001</v>
       </c>
       <c r="AG21" t="n">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="AH21" t="n">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="AI21" t="b">
         <v>0</v>
@@ -3401,11 +3397,13 @@
         <v>0</v>
       </c>
       <c r="AN21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>2313</v>
+      </c>
       <c r="AP21" t="n">
-        <v>244.55</v>
+        <v>2628.42</v>
       </c>
     </row>
     <row r="22">
@@ -3439,7 +3437,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -3471,7 +3469,7 @@
         <v>79</v>
       </c>
       <c r="R22" t="n">
-        <v>3330822</v>
+        <v>3315166</v>
       </c>
       <c r="S22" t="n">
         <v>79.8</v>
@@ -3556,12 +3554,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3570,7 +3568,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>35.8</v>
+        <v>36.4</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3579,15 +3577,15 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>23519000</v>
+        <v>7556450</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K23" t="b">
         <v>1</v>
@@ -3596,7 +3594,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>23519000</v>
+        <v>7556450</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -3605,61 +3603,61 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>521</v>
+        <v>269</v>
       </c>
       <c r="Q23" t="n">
-        <v>521</v>
+        <v>269</v>
       </c>
       <c r="R23" t="n">
-        <v>31814660</v>
+        <v>25315766</v>
       </c>
       <c r="S23" t="n">
-        <v>520</v>
+        <v>266.3</v>
       </c>
       <c r="T23" t="n">
-        <v>578.65</v>
+        <v>286.55</v>
       </c>
       <c r="U23" t="n">
-        <v>581.25</v>
+        <v>288.3</v>
       </c>
       <c r="V23" t="n">
-        <v>567.2416666666667</v>
+        <v>266.5</v>
       </c>
       <c r="W23" t="n">
-        <v>-20.42398382588908</v>
+        <v>-6.439246733244204</v>
       </c>
       <c r="X23" t="n">
-        <v>-8.987720670222682</v>
+        <v>-3.198326649822184</v>
       </c>
       <c r="Y23" t="n">
-        <v>-11.4362631556664</v>
+        <v>-3.24092008342202</v>
       </c>
       <c r="Z23" t="n">
-        <v>-14.26674574116766</v>
+        <v>-4.489412957966038</v>
       </c>
       <c r="AA23" t="b">
         <v>1</v>
       </c>
       <c r="AB23" t="n">
-        <v>-0.09075043630017454</v>
+        <v>-0.1151315789473685</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.02761341222879676</v>
+        <v>0.2658823529411765</v>
       </c>
       <c r="AD23" t="n">
-        <v>-0.05510325472296396</v>
+        <v>-0.07948439737015789</v>
       </c>
       <c r="AE23" t="n">
-        <v>-0.08037957586749211</v>
+        <v>0.1578893648448876</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.02527632114452816</v>
+        <v>-0.2373737622150455</v>
       </c>
       <c r="AG23" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AH23" t="n">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="AI23" t="b">
         <v>0</v>
@@ -3677,11 +3675,13 @@
         <v>1</v>
       </c>
       <c r="AN23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO23" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>305.58</v>
+      </c>
       <c r="AP23" t="n">
-        <v>640.6799999999999</v>
+        <v>329.47</v>
       </c>
     </row>
     <row r="24">
@@ -3692,12 +3692,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3706,96 +3706,96 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>35.6</v>
+        <v>35.8</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>969000</v>
+        <v>23519000</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="K24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="b">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>919000</v>
+        <v>23519000</v>
       </c>
       <c r="N24" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0544069640914037</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2250</v>
+        <v>521</v>
       </c>
       <c r="Q24" t="n">
-        <v>2250</v>
+        <v>521</v>
       </c>
       <c r="R24" t="n">
-        <v>1223000</v>
+        <v>31214647</v>
       </c>
       <c r="S24" t="n">
-        <v>2321</v>
+        <v>520</v>
       </c>
       <c r="T24" t="n">
-        <v>2343.5</v>
+        <v>578.65</v>
       </c>
       <c r="U24" t="n">
-        <v>2361</v>
+        <v>581.25</v>
       </c>
       <c r="V24" t="n">
-        <v>2100.230332438151</v>
+        <v>567.2416666666667</v>
       </c>
       <c r="W24" t="n">
-        <v>-2.166083020384121</v>
+        <v>-20.42398382588908</v>
       </c>
       <c r="X24" t="n">
-        <v>3.145393600799783</v>
+        <v>-8.987720670222682</v>
       </c>
       <c r="Y24" t="n">
-        <v>-5.311476621183904</v>
+        <v>-11.4362631556664</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.524106016444781</v>
+        <v>-14.26674574116766</v>
       </c>
       <c r="AA24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB24" t="n">
-        <v>-0.1346153846153846</v>
+        <v>-0.09075043630017454</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.791094203859015</v>
+        <v>0.02761341222879676</v>
       </c>
       <c r="AD24" t="n">
-        <v>-0.098968203038174</v>
+        <v>-0.05510325472296396</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.6831012157627261</v>
+        <v>-0.08037957586749211</v>
       </c>
       <c r="AF24" t="n">
-        <v>-0.7820694188009001</v>
+        <v>0.02527632114452816</v>
       </c>
       <c r="AG24" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="AH24" t="n">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="AI24" t="b">
         <v>0</v>
@@ -3810,16 +3810,14 @@
         <v>0</v>
       </c>
       <c r="AM24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>2313</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO24" t="inlineStr"/>
       <c r="AP24" t="n">
-        <v>2628.42</v>
+        <v>640.6799999999999</v>
       </c>
     </row>
     <row r="25">
@@ -3853,7 +3851,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -3861,7 +3859,7 @@
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K25" t="b">
         <v>1</v>
@@ -3885,7 +3883,7 @@
         <v>1280</v>
       </c>
       <c r="R25" t="n">
-        <v>16360844</v>
+        <v>15426252</v>
       </c>
       <c r="S25" t="n">
         <v>1434</v>
@@ -3989,7 +3987,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -4021,7 +4019,7 @@
         <v>5860</v>
       </c>
       <c r="R26" t="n">
-        <v>2418770</v>
+        <v>2354701</v>
       </c>
       <c r="S26" t="n">
         <v>6237</v>
@@ -4125,7 +4123,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -4157,7 +4155,7 @@
         <v>4750</v>
       </c>
       <c r="R27" t="n">
-        <v>4884266</v>
+        <v>4442420</v>
       </c>
       <c r="S27" t="n">
         <v>4965</v>
@@ -4261,7 +4259,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -4293,7 +4291,7 @@
         <v>3495</v>
       </c>
       <c r="R28" t="n">
-        <v>1220036</v>
+        <v>1150956</v>
       </c>
       <c r="S28" t="n">
         <v>3567</v>
@@ -4397,7 +4395,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -4429,7 +4427,7 @@
         <v>161.5</v>
       </c>
       <c r="R29" t="n">
-        <v>12632328</v>
+        <v>12578932</v>
       </c>
       <c r="S29" t="n">
         <v>162</v>
@@ -4512,12 +4510,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4526,7 +4524,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>30.6</v>
+        <v>30.4</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4535,15 +4533,15 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>852000</v>
+        <v>6537000</v>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="K30" t="b">
         <v>0</v>
@@ -4552,7 +4550,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>852000</v>
+        <v>6537000</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -4561,61 +4559,61 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>7430</v>
+        <v>3130</v>
       </c>
       <c r="Q30" t="n">
-        <v>7430</v>
+        <v>3130</v>
       </c>
       <c r="R30" t="n">
-        <v>2365460</v>
+        <v>2691731</v>
       </c>
       <c r="S30" t="n">
-        <v>7669</v>
+        <v>3196</v>
       </c>
       <c r="T30" t="n">
-        <v>7992.5</v>
+        <v>3363.75</v>
       </c>
       <c r="U30" t="n">
-        <v>8040.25</v>
+        <v>3380.75</v>
       </c>
       <c r="V30" t="n">
-        <v>6463</v>
+        <v>3185.9912109375</v>
       </c>
       <c r="W30" t="n">
-        <v>-30.32926562784814</v>
+        <v>-64.94596194307451</v>
       </c>
       <c r="X30" t="n">
-        <v>113.5701033116136</v>
+        <v>-33.7312883593824</v>
       </c>
       <c r="Y30" t="n">
-        <v>-143.8993689394617</v>
+        <v>-31.2146735836921</v>
       </c>
       <c r="Z30" t="n">
-        <v>-140.2217805557706</v>
+        <v>-32.99125700943229</v>
       </c>
       <c r="AA30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB30" t="n">
-        <v>-0.1138938580799046</v>
+        <v>-0.09798270893371763</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.254931714719272</v>
+        <v>0.5028965429281285</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.07824667650269401</v>
+        <v>-0.06233552735650705</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.146938726622983</v>
+        <v>0.3949035548318396</v>
       </c>
       <c r="AF30" t="n">
-        <v>-1.225185403125677</v>
+        <v>-0.4572390821883466</v>
       </c>
       <c r="AG30" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AH30" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="AI30" t="b">
         <v>0</v>
@@ -4630,14 +4628,16 @@
         <v>0</v>
       </c>
       <c r="AM30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO30" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>3486.82</v>
+      </c>
       <c r="AP30" t="n">
-        <v>9117.110000000001</v>
+        <v>3801.05</v>
       </c>
     </row>
     <row r="31">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -4703,7 +4703,7 @@
         <v>207.5</v>
       </c>
       <c r="R31" t="n">
-        <v>2029174</v>
+        <v>1975464</v>
       </c>
       <c r="S31" t="n">
         <v>217.7</v>
@@ -4807,7 +4807,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -4839,7 +4839,7 @@
         <v>97</v>
       </c>
       <c r="R32" t="n">
-        <v>29635220</v>
+        <v>29478451</v>
       </c>
       <c r="S32" t="n">
         <v>98.08000030517579</v>
@@ -4943,7 +4943,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -4975,7 +4975,7 @@
         <v>1950</v>
       </c>
       <c r="R33" t="n">
-        <v>5074575</v>
+        <v>4784282</v>
       </c>
       <c r="S33" t="n">
         <v>1887</v>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -5113,7 +5113,7 @@
         <v>1760</v>
       </c>
       <c r="R34" t="n">
-        <v>4381870</v>
+        <v>4245335</v>
       </c>
       <c r="S34" t="n">
         <v>1819</v>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -5249,7 +5249,7 @@
         <v>1140</v>
       </c>
       <c r="R35" t="n">
-        <v>2087205</v>
+        <v>2054287</v>
       </c>
       <c r="S35" t="n">
         <v>1114</v>
@@ -5357,11 +5357,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>5233000</v>
+        <v>5306000</v>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
@@ -5374,13 +5374,13 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>5143000</v>
+        <v>5233000</v>
       </c>
       <c r="N36" t="n">
-        <v>90000</v>
+        <v>73000</v>
       </c>
       <c r="O36" t="n">
-        <v>0.0174995139023916</v>
+        <v>0.01394993311675903</v>
       </c>
       <c r="P36" t="n">
         <v>3960</v>
@@ -5389,7 +5389,7 @@
         <v>3960</v>
       </c>
       <c r="R36" t="n">
-        <v>13034792</v>
+        <v>12002110</v>
       </c>
       <c r="S36" t="n">
         <v>4054</v>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -5527,7 +5527,7 @@
         <v>150</v>
       </c>
       <c r="R37" t="n">
-        <v>6905267</v>
+        <v>6821080</v>
       </c>
       <c r="S37" t="n">
         <v>153.9</v>
@@ -5633,7 +5633,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -5665,7 +5665,7 @@
         <v>122.5</v>
       </c>
       <c r="R38" t="n">
-        <v>126613595</v>
+        <v>125290236</v>
       </c>
       <c r="S38" t="n">
         <v>125.7</v>
@@ -5748,12 +5748,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5762,96 +5762,96 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>24.6</v>
+        <v>25</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>7582000</v>
+        <v>223900</v>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="K39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="b">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>7582000</v>
+        <v>201900</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>0.1089648340762754</v>
       </c>
       <c r="P39" t="n">
-        <v>1510</v>
+        <v>16015</v>
       </c>
       <c r="Q39" t="n">
-        <v>1510</v>
+        <v>16015</v>
       </c>
       <c r="R39" t="n">
-        <v>18473608</v>
+        <v>355762</v>
       </c>
       <c r="S39" t="n">
-        <v>1572</v>
+        <v>16090</v>
       </c>
       <c r="T39" t="n">
-        <v>1783</v>
+        <v>17550</v>
       </c>
       <c r="U39" t="n">
-        <v>1802.5</v>
+        <v>17763.25</v>
       </c>
       <c r="V39" t="n">
-        <v>1763.5</v>
+        <v>17252.83333333333</v>
       </c>
       <c r="W39" t="n">
-        <v>-82.43149098345225</v>
+        <v>-616.1500488829661</v>
       </c>
       <c r="X39" t="n">
-        <v>-50.33238503907849</v>
+        <v>-520.9833715903321</v>
       </c>
       <c r="Y39" t="n">
-        <v>-32.09910594437376</v>
+        <v>-95.16667729263395</v>
       </c>
       <c r="Z39" t="n">
-        <v>-33.87387370665132</v>
+        <v>-143.733134191985</v>
       </c>
       <c r="AA39" t="b">
         <v>1</v>
       </c>
       <c r="AB39" t="n">
-        <v>-0.2052631578947368</v>
+        <v>-0.2103057199211046</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.01003344481605351</v>
+        <v>0.2405112316034081</v>
       </c>
       <c r="AD39" t="n">
-        <v>-0.1696159763175262</v>
+        <v>-0.174658538343894</v>
       </c>
       <c r="AE39" t="n">
-        <v>-0.09795954328023537</v>
+        <v>0.1325182435071193</v>
       </c>
       <c r="AF39" t="n">
-        <v>-0.07165643303729086</v>
+        <v>-0.3071767818510133</v>
       </c>
       <c r="AG39" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AH39" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="AI39" t="b">
         <v>0</v>
@@ -5869,11 +5869,13 @@
         <v>1</v>
       </c>
       <c r="AN39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO39" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>17104.02</v>
+      </c>
       <c r="AP39" t="n">
-        <v>2197.37</v>
+        <v>21450.79</v>
       </c>
     </row>
     <row r="40">
@@ -5884,12 +5886,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5898,7 +5900,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>22.8</v>
+        <v>24.6</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5907,24 +5909,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>654000</v>
+        <v>7582000</v>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="K40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" t="b">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>654000</v>
+        <v>7582000</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -5933,61 +5935,61 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>420.5</v>
+        <v>1510</v>
       </c>
       <c r="Q40" t="n">
-        <v>420.5</v>
+        <v>1510</v>
       </c>
       <c r="R40" t="n">
-        <v>4114718</v>
+        <v>16664194</v>
       </c>
       <c r="S40" t="n">
-        <v>449.8</v>
+        <v>1572</v>
       </c>
       <c r="T40" t="n">
-        <v>495.825</v>
+        <v>1783</v>
       </c>
       <c r="U40" t="n">
-        <v>499.65</v>
+        <v>1802.5</v>
       </c>
       <c r="V40" t="n">
-        <v>462.2666666666667</v>
+        <v>1763.5</v>
       </c>
       <c r="W40" t="n">
-        <v>-19.62717931946963</v>
+        <v>-82.43149098345225</v>
       </c>
       <c r="X40" t="n">
-        <v>-9.339828995562229</v>
+        <v>-50.33238503907849</v>
       </c>
       <c r="Y40" t="n">
-        <v>-10.2873503239074</v>
+        <v>-32.09910594437376</v>
       </c>
       <c r="Z40" t="n">
-        <v>-9.364113313695203</v>
+        <v>-33.87387370665132</v>
       </c>
       <c r="AA40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB40" t="n">
-        <v>-0.1539235412474849</v>
+        <v>-0.2052631578947368</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.3970099667774087</v>
+        <v>0.01003344481605351</v>
       </c>
       <c r="AD40" t="n">
-        <v>-0.1182763596702743</v>
+        <v>-0.1696159763175262</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.2890169786811199</v>
+        <v>-0.09795954328023537</v>
       </c>
       <c r="AF40" t="n">
-        <v>-0.4072933383513941</v>
+        <v>-0.07165643303729086</v>
       </c>
       <c r="AG40" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AH40" t="n">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="AI40" t="b">
         <v>0</v>
@@ -6002,14 +6004,14 @@
         <v>0</v>
       </c>
       <c r="AM40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN40" t="b">
         <v>0</v>
       </c>
       <c r="AO40" t="inlineStr"/>
       <c r="AP40" t="n">
-        <v>590.29</v>
+        <v>2197.37</v>
       </c>
     </row>
     <row r="41">
@@ -6020,12 +6022,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>新日興</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6034,7 +6036,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6043,15 +6045,15 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1740000</v>
+        <v>654000</v>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K41" t="b">
         <v>0</v>
@@ -6060,7 +6062,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1740000</v>
+        <v>654000</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -6069,61 +6071,61 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>157.5</v>
+        <v>420.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>157.5</v>
+        <v>420.5</v>
       </c>
       <c r="R41" t="n">
-        <v>7250912</v>
+        <v>3831834</v>
       </c>
       <c r="S41" t="n">
-        <v>172.7</v>
+        <v>449.8</v>
       </c>
       <c r="T41" t="n">
-        <v>173</v>
+        <v>495.825</v>
       </c>
       <c r="U41" t="n">
-        <v>173.95</v>
+        <v>499.65</v>
       </c>
       <c r="V41" t="n">
-        <v>183.7011975606283</v>
+        <v>462.2666666666667</v>
       </c>
       <c r="W41" t="n">
-        <v>-2.56679779765625</v>
+        <v>-19.62717931946963</v>
       </c>
       <c r="X41" t="n">
-        <v>-1.628288338966192</v>
+        <v>-9.339828995562229</v>
       </c>
       <c r="Y41" t="n">
-        <v>-0.9385094586900582</v>
+        <v>-10.2873503239074</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.702390597453298</v>
+        <v>-9.364113313695203</v>
       </c>
       <c r="AA41" t="b">
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>-0.1076487252124646</v>
+        <v>-0.1539235412474849</v>
       </c>
       <c r="AC41" t="n">
-        <v>-0.04745346402203299</v>
+        <v>0.3970099667774087</v>
       </c>
       <c r="AD41" t="n">
-        <v>-0.07200154363525402</v>
+        <v>-0.1182763596702743</v>
       </c>
       <c r="AE41" t="n">
-        <v>-0.1554464521183219</v>
+        <v>0.2890169786811199</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.08344490848306785</v>
+        <v>-0.4072933383513941</v>
       </c>
       <c r="AG41" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AH41" t="n">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="AI41" t="b">
         <v>0</v>
@@ -6141,13 +6143,11 @@
         <v>0</v>
       </c>
       <c r="AN41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>168.21</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO41" t="inlineStr"/>
       <c r="AP41" t="n">
-        <v>190.32</v>
+        <v>590.29</v>
       </c>
     </row>
     <row r="42">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>新日興</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6172,7 +6172,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>21.6</v>
+        <v>22.6</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6181,15 +6181,15 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1000</v>
+        <v>1740000</v>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="K42" t="b">
         <v>0</v>
@@ -6198,7 +6198,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1000</v>
+        <v>1740000</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -6207,61 +6207,61 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>441</v>
+        <v>157.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>441</v>
+        <v>157.5</v>
       </c>
       <c r="R42" t="n">
-        <v>43888538</v>
+        <v>7078965</v>
       </c>
       <c r="S42" t="n">
-        <v>425.5</v>
+        <v>172.7</v>
       </c>
       <c r="T42" t="n">
-        <v>481</v>
+        <v>173</v>
       </c>
       <c r="U42" t="n">
-        <v>484.7</v>
+        <v>173.95</v>
       </c>
       <c r="V42" t="n">
-        <v>487.9833333333333</v>
+        <v>183.7011975606283</v>
       </c>
       <c r="W42" t="n">
-        <v>-21.52003481416489</v>
+        <v>-2.56679779765625</v>
       </c>
       <c r="X42" t="n">
-        <v>-16.88969822185205</v>
+        <v>-1.628288338966192</v>
       </c>
       <c r="Y42" t="n">
-        <v>-4.63033659231284</v>
+        <v>-0.9385094586900582</v>
       </c>
       <c r="Z42" t="n">
-        <v>-8.7200296522578</v>
+        <v>0.702390597453298</v>
       </c>
       <c r="AA42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>-0.1436893203883495</v>
+        <v>-0.1076487252124646</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.2475247524752475</v>
+        <v>-0.04745346402203299</v>
       </c>
       <c r="AD42" t="n">
-        <v>-0.1080421388111389</v>
+        <v>-0.07200154363525402</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.1395317643789586</v>
+        <v>-0.1554464521183219</v>
       </c>
       <c r="AF42" t="n">
-        <v>-0.2475739031900975</v>
+        <v>0.08344490848306785</v>
       </c>
       <c r="AG42" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AH42" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="AI42" t="b">
         <v>0</v>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="AM42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="b">
         <v>1</v>
       </c>
       <c r="AO42" t="n">
-        <v>493.92</v>
+        <v>168.21</v>
       </c>
       <c r="AP42" t="n">
-        <v>545.11</v>
+        <v>190.32</v>
       </c>
     </row>
     <row r="43">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6310,7 +6310,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>18.8</v>
+        <v>21.6</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6319,15 +6319,15 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>470000</v>
+        <v>1000</v>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="K43" t="b">
         <v>0</v>
@@ -6336,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>470000</v>
+        <v>1000</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -6345,61 +6345,61 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2910</v>
+        <v>441</v>
       </c>
       <c r="Q43" t="n">
-        <v>2910</v>
+        <v>441</v>
       </c>
       <c r="R43" t="n">
-        <v>510702</v>
+        <v>42979384</v>
       </c>
       <c r="S43" t="n">
-        <v>3073</v>
+        <v>425.5</v>
       </c>
       <c r="T43" t="n">
-        <v>3128.5</v>
+        <v>481</v>
       </c>
       <c r="U43" t="n">
-        <v>3156.75</v>
+        <v>484.7</v>
       </c>
       <c r="V43" t="n">
-        <v>3060.5</v>
+        <v>487.9833333333333</v>
       </c>
       <c r="W43" t="n">
-        <v>-53.34120822180239</v>
+        <v>-21.52003481416489</v>
       </c>
       <c r="X43" t="n">
-        <v>-31.11294016918112</v>
+        <v>-16.88969822185205</v>
       </c>
       <c r="Y43" t="n">
-        <v>-22.22826805262127</v>
+        <v>-4.63033659231284</v>
       </c>
       <c r="Z43" t="n">
-        <v>-7.76191389779396</v>
+        <v>-8.7200296522578</v>
       </c>
       <c r="AA43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB43" t="n">
-        <v>-0.162589928057554</v>
+        <v>-0.1436893203883495</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.2278481012658229</v>
+        <v>0.2475247524752475</v>
       </c>
       <c r="AD43" t="n">
-        <v>-0.1269427464803434</v>
+        <v>-0.1080421388111389</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.119855113169534</v>
+        <v>0.1395317643789586</v>
       </c>
       <c r="AF43" t="n">
-        <v>-0.2467978596498774</v>
+        <v>-0.2475739031900975</v>
       </c>
       <c r="AG43" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AH43" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AI43" t="b">
         <v>0</v>
@@ -6414,16 +6414,16 @@
         <v>0</v>
       </c>
       <c r="AM43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN43" t="b">
         <v>1</v>
       </c>
       <c r="AO43" t="n">
-        <v>3160.26</v>
+        <v>493.92</v>
       </c>
       <c r="AP43" t="n">
-        <v>3540</v>
+        <v>545.11</v>
       </c>
     </row>
     <row r="44">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6448,7 +6448,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>18.2</v>
+        <v>18.8</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6457,15 +6457,15 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1000</v>
+        <v>470000</v>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="K44" t="b">
         <v>0</v>
@@ -6474,7 +6474,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1000</v>
+        <v>470000</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -6483,61 +6483,61 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>814</v>
+        <v>2910</v>
       </c>
       <c r="Q44" t="n">
-        <v>814</v>
+        <v>2910</v>
       </c>
       <c r="R44" t="n">
-        <v>11961472</v>
+        <v>481659</v>
       </c>
       <c r="S44" t="n">
-        <v>838</v>
+        <v>3073</v>
       </c>
       <c r="T44" t="n">
-        <v>999</v>
+        <v>3128.5</v>
       </c>
       <c r="U44" t="n">
-        <v>1005.8</v>
+        <v>3156.75</v>
       </c>
       <c r="V44" t="n">
-        <v>958.7333333333333</v>
+        <v>3060.5</v>
       </c>
       <c r="W44" t="n">
-        <v>-57.42235528703225</v>
+        <v>-53.34120822180239</v>
       </c>
       <c r="X44" t="n">
-        <v>-30.3095163342285</v>
+        <v>-31.11294016918112</v>
       </c>
       <c r="Y44" t="n">
-        <v>-27.11283895280375</v>
+        <v>-22.22826805262127</v>
       </c>
       <c r="Z44" t="n">
-        <v>-31.16218302759852</v>
+        <v>-7.76191389779396</v>
       </c>
       <c r="AA44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>-0.1431578947368422</v>
+        <v>-0.162589928057554</v>
       </c>
       <c r="AC44" t="n">
-        <v>-0.05787037037037035</v>
+        <v>0.2278481012658229</v>
       </c>
       <c r="AD44" t="n">
-        <v>-0.1075107131596316</v>
+        <v>-0.1269427464803434</v>
       </c>
       <c r="AE44" t="n">
-        <v>-0.1658633584666592</v>
+        <v>0.119855113169534</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.05835264530702766</v>
+        <v>-0.2467978596498774</v>
       </c>
       <c r="AG44" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="AH44" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="AI44" t="b">
         <v>0</v>
@@ -6552,14 +6552,16 @@
         <v>0</v>
       </c>
       <c r="AM44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO44" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>3160.26</v>
+      </c>
       <c r="AP44" t="n">
-        <v>1142.74</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="45">
@@ -6570,12 +6572,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6584,7 +6586,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>17.6</v>
+        <v>18.2</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6593,7 +6595,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -6601,7 +6603,7 @@
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="K45" t="b">
         <v>0</v>
@@ -6619,61 +6621,61 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>1955</v>
+        <v>814</v>
       </c>
       <c r="Q45" t="n">
-        <v>1955</v>
+        <v>814</v>
       </c>
       <c r="R45" t="n">
-        <v>3620562</v>
+        <v>11570704</v>
       </c>
       <c r="S45" t="n">
-        <v>1985</v>
+        <v>838</v>
       </c>
       <c r="T45" t="n">
-        <v>2153</v>
+        <v>999</v>
       </c>
       <c r="U45" t="n">
-        <v>2171.5</v>
+        <v>1005.8</v>
       </c>
       <c r="V45" t="n">
-        <v>2129.916666666667</v>
+        <v>958.7333333333333</v>
       </c>
       <c r="W45" t="n">
-        <v>-69.92818045076706</v>
+        <v>-57.42235528703225</v>
       </c>
       <c r="X45" t="n">
-        <v>-44.00523729951917</v>
+        <v>-30.3095163342285</v>
       </c>
       <c r="Y45" t="n">
-        <v>-25.92294315124789</v>
+        <v>-27.11283895280375</v>
       </c>
       <c r="Z45" t="n">
-        <v>-30.15236553389909</v>
+        <v>-31.16218302759852</v>
       </c>
       <c r="AA45" t="b">
         <v>1</v>
       </c>
       <c r="AB45" t="n">
-        <v>-0.1591397849462366</v>
+        <v>-0.1431578947368422</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.06539509536784749</v>
+        <v>-0.05787037037037035</v>
       </c>
       <c r="AD45" t="n">
-        <v>-0.123492603369026</v>
+        <v>-0.1075107131596316</v>
       </c>
       <c r="AE45" t="n">
-        <v>-0.04259789272844139</v>
+        <v>-0.1658633584666592</v>
       </c>
       <c r="AF45" t="n">
-        <v>-0.08089471064058462</v>
+        <v>0.05835264530702766</v>
       </c>
       <c r="AG45" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AH45" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AI45" t="b">
         <v>0</v>
@@ -6691,13 +6693,11 @@
         <v>1</v>
       </c>
       <c r="AN45" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>2248.25</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO45" t="inlineStr"/>
       <c r="AP45" t="n">
-        <v>2503.42</v>
+        <v>1142.74</v>
       </c>
     </row>
     <row r="46">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6722,7 +6722,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>17.4</v>
+        <v>17.6</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6731,15 +6731,15 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>2504000</v>
+        <v>1000</v>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="K46" t="b">
         <v>0</v>
@@ -6748,7 +6748,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>2504000</v>
+        <v>1000</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -6757,61 +6757,61 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>4790</v>
+        <v>1955</v>
       </c>
       <c r="Q46" t="n">
-        <v>4790</v>
+        <v>1955</v>
       </c>
       <c r="R46" t="n">
-        <v>857431</v>
+        <v>3549040</v>
       </c>
       <c r="S46" t="n">
-        <v>4895</v>
+        <v>1985</v>
       </c>
       <c r="T46" t="n">
-        <v>5326.5</v>
+        <v>2153</v>
       </c>
       <c r="U46" t="n">
-        <v>5368</v>
+        <v>2171.5</v>
       </c>
       <c r="V46" t="n">
-        <v>5522.75</v>
+        <v>2129.916666666667</v>
       </c>
       <c r="W46" t="n">
-        <v>-181.4637122785407</v>
+        <v>-69.92818045076706</v>
       </c>
       <c r="X46" t="n">
-        <v>-92.32264159023076</v>
+        <v>-44.00523729951917</v>
       </c>
       <c r="Y46" t="n">
-        <v>-89.14107068830994</v>
+        <v>-25.92294315124789</v>
       </c>
       <c r="Z46" t="n">
-        <v>-92.87367995604467</v>
+        <v>-30.15236553389909</v>
       </c>
       <c r="AA46" t="b">
         <v>1</v>
       </c>
       <c r="AB46" t="n">
-        <v>-0.1476868327402135</v>
+        <v>-0.1591397849462366</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>0.06539509536784749</v>
       </c>
       <c r="AD46" t="n">
-        <v>-0.112039651163003</v>
+        <v>-0.123492603369026</v>
       </c>
       <c r="AE46" t="n">
-        <v>-0.1079929880962889</v>
+        <v>-0.04259789272844139</v>
       </c>
       <c r="AF46" t="n">
-        <v>-0.004046663066714085</v>
+        <v>-0.08089471064058462</v>
       </c>
       <c r="AG46" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AH46" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="AI46" t="b">
         <v>0</v>
@@ -6829,11 +6829,13 @@
         <v>1</v>
       </c>
       <c r="AN46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO46" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>2248.25</v>
+      </c>
       <c r="AP46" t="n">
-        <v>5979.74</v>
+        <v>2503.42</v>
       </c>
     </row>
     <row r="47">
@@ -6844,12 +6846,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6858,7 +6860,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>16.8</v>
+        <v>17.4</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6867,15 +6869,15 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>957000</v>
+        <v>2504000</v>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="K47" t="b">
         <v>0</v>
@@ -6884,7 +6886,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>957000</v>
+        <v>2504000</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -6893,61 +6895,61 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>467.5</v>
+        <v>4790</v>
       </c>
       <c r="Q47" t="n">
-        <v>467.5</v>
+        <v>4790</v>
       </c>
       <c r="R47" t="n">
-        <v>782307</v>
+        <v>807435</v>
       </c>
       <c r="S47" t="n">
-        <v>465.1</v>
+        <v>4895</v>
       </c>
       <c r="T47" t="n">
-        <v>536.175</v>
+        <v>5326.5</v>
       </c>
       <c r="U47" t="n">
-        <v>542.3</v>
+        <v>5368</v>
       </c>
       <c r="V47" t="n">
-        <v>545.025</v>
+        <v>5522.75</v>
       </c>
       <c r="W47" t="n">
-        <v>-29.813879631237</v>
+        <v>-181.4637122785407</v>
       </c>
       <c r="X47" t="n">
-        <v>-20.50011714195697</v>
+        <v>-92.32264159023076</v>
       </c>
       <c r="Y47" t="n">
-        <v>-9.313762489280034</v>
+        <v>-89.14107068830994</v>
       </c>
       <c r="Z47" t="n">
-        <v>-12.61019885582612</v>
+        <v>-92.87367995604467</v>
       </c>
       <c r="AA47" t="b">
         <v>1</v>
       </c>
       <c r="AB47" t="n">
-        <v>-0.2076271186440678</v>
+        <v>-0.1476868327402135</v>
       </c>
       <c r="AC47" t="n">
-        <v>0.2158647594278285</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>-0.1719799370668572</v>
+        <v>-0.112039651163003</v>
       </c>
       <c r="AE47" t="n">
-        <v>0.1078717713315396</v>
+        <v>-0.1079929880962889</v>
       </c>
       <c r="AF47" t="n">
-        <v>-0.2798517083983968</v>
+        <v>-0.004046663066714085</v>
       </c>
       <c r="AG47" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="AH47" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="AI47" t="b">
         <v>0</v>
@@ -6969,7 +6971,7 @@
       </c>
       <c r="AO47" t="inlineStr"/>
       <c r="AP47" t="n">
-        <v>635.29</v>
+        <v>5979.74</v>
       </c>
     </row>
     <row r="48">
@@ -6980,12 +6982,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6994,7 +6996,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>16.6</v>
+        <v>16.8</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -7003,15 +7005,15 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>201900</v>
+        <v>957000</v>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="K48" t="b">
         <v>0</v>
@@ -7020,7 +7022,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>201900</v>
+        <v>957000</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -7029,61 +7031,61 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>16015</v>
+        <v>467.5</v>
       </c>
       <c r="Q48" t="n">
-        <v>16015</v>
+        <v>467.5</v>
       </c>
       <c r="R48" t="n">
-        <v>373678</v>
+        <v>756851</v>
       </c>
       <c r="S48" t="n">
-        <v>16090</v>
+        <v>465.1</v>
       </c>
       <c r="T48" t="n">
-        <v>17550</v>
+        <v>536.175</v>
       </c>
       <c r="U48" t="n">
-        <v>17763.25</v>
+        <v>542.3</v>
       </c>
       <c r="V48" t="n">
-        <v>17252.83333333333</v>
+        <v>545.025</v>
       </c>
       <c r="W48" t="n">
-        <v>-616.1500488829661</v>
+        <v>-29.813879631237</v>
       </c>
       <c r="X48" t="n">
-        <v>-520.9833715903321</v>
+        <v>-20.50011714195697</v>
       </c>
       <c r="Y48" t="n">
-        <v>-95.16667729263395</v>
+        <v>-9.313762489280034</v>
       </c>
       <c r="Z48" t="n">
-        <v>-143.733134191985</v>
+        <v>-12.61019885582612</v>
       </c>
       <c r="AA48" t="b">
         <v>1</v>
       </c>
       <c r="AB48" t="n">
-        <v>-0.2103057199211046</v>
+        <v>-0.2076271186440678</v>
       </c>
       <c r="AC48" t="n">
-        <v>0.2405112316034081</v>
+        <v>0.2158647594278285</v>
       </c>
       <c r="AD48" t="n">
-        <v>-0.174658538343894</v>
+        <v>-0.1719799370668572</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.1325182435071193</v>
+        <v>0.1078717713315396</v>
       </c>
       <c r="AF48" t="n">
-        <v>-0.3071767818510133</v>
+        <v>-0.2798517083983968</v>
       </c>
       <c r="AG48" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AH48" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AI48" t="b">
         <v>0</v>
@@ -7101,13 +7103,11 @@
         <v>1</v>
       </c>
       <c r="AN48" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>17104.02</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO48" t="inlineStr"/>
       <c r="AP48" t="n">
-        <v>21450.79</v>
+        <v>635.29</v>
       </c>
     </row>
     <row r="49">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -7173,7 +7173,7 @@
         <v>1735</v>
       </c>
       <c r="R49" t="n">
-        <v>5643357</v>
+        <v>5323011</v>
       </c>
       <c r="S49" t="n">
         <v>1872</v>
@@ -7277,11 +7277,11 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>378000</v>
+        <v>302000</v>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
@@ -7294,13 +7294,13 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>478000</v>
+        <v>378000</v>
       </c>
       <c r="N50" t="n">
-        <v>-100000</v>
+        <v>-76000</v>
       </c>
       <c r="O50" t="n">
-        <v>-0.2092050209205021</v>
+        <v>-0.201058201058201</v>
       </c>
       <c r="P50" t="n">
         <v>775</v>
@@ -7309,7 +7309,7 @@
         <v>775</v>
       </c>
       <c r="R50" t="n">
-        <v>1494384</v>
+        <v>1382559</v>
       </c>
       <c r="S50" t="n">
         <v>781.2</v>
@@ -7415,11 +7415,11 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20261027</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>85000</v>
+        <v>77000</v>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
@@ -7432,13 +7432,13 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>93000</v>
+        <v>85000</v>
       </c>
       <c r="N51" t="n">
         <v>-8000</v>
       </c>
       <c r="O51" t="n">
-        <v>-0.08602150537634409</v>
+        <v>-0.09411764705882353</v>
       </c>
       <c r="P51" t="n">
         <v>4775</v>
@@ -7447,7 +7447,7 @@
         <v>4775</v>
       </c>
       <c r="R51" t="n">
-        <v>568234</v>
+        <v>541440</v>
       </c>
       <c r="S51" t="n">
         <v>4859</v>
